--- a/output/pdf_financials_xlsx/IPD.xlsx
+++ b/output/pdf_financials_xlsx/IPD.xlsx
@@ -5555,49 +5555,49 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.019882</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.035137</v>
+        <v>-0.026897</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.018128</v>
+        <v>0.022461</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.027747</v>
+        <v>0.020077</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.046149</v>
+        <v>0.022142</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.011651</v>
+        <v>-0.125465</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.145371</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.002754</v>
+        <v>-0.132847</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.002408</v>
+        <v>-0.273058</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.283333</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.378493</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.379428</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.366017</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-0.365536</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-0.378113</v>
       </c>
     </row>
     <row r="92">
@@ -9898,7 +9898,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11354,7 +11358,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IPD.xlsx
+++ b/output/pdf_financials_xlsx/IPD.xlsx
@@ -2327,40 +2327,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.11823</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.387668</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.291042</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.306386</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.153508</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.425437</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.290152</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.27827</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.381105</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.398174</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.322647</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.259524</v>
@@ -2369,10 +2369,10 @@
         <v>0.234495</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.273073</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.157623</v>
       </c>
     </row>
     <row r="35">
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.11823</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.387668</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.088932</v>
+        <v>0.379974</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.142893</v>
+        <v>0.449279</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.259844</v>
+        <v>0.413352</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.261063</v>
+        <v>0.446163</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.057843</v>
+        <v>0.48328</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.044504</v>
+        <v>0.334656</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.064929</v>
+        <v>0.343199</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.031238</v>
+        <v>0.412343</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.398174</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.322647</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.259524</v>
@@ -2479,10 +2479,10 @@
         <v>0.234495</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.273073</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.157623</v>
       </c>
     </row>
     <row r="37">
@@ -3097,40 +3097,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.173328</v>
+        <v>0.055098</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.426537</v>
+        <v>0.038869</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.404636</v>
+        <v>0.113594</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.332341</v>
+        <v>0.025955</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.174995</v>
+        <v>0.021487</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.223473</v>
+        <v>0.038373</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.464762</v>
+        <v>0.039325</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.319667</v>
+        <v>0.029515</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.363368</v>
+        <v>0.08509799999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.407012</v>
+        <v>0.025907</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.405728</v>
+        <v>0.007554</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.445456</v>
+        <v>0.122809</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.006258</v>
@@ -3139,10 +3139,10 @@
         <v>0.017016</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.283929</v>
+        <v>0.010856</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.180278</v>
+        <v>0.022655</v>
       </c>
     </row>
     <row r="49">
@@ -7411,22 +7411,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048143</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048797</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.049992</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.044373</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046044</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04706</v>
       </c>
     </row>
     <row r="125">
@@ -7468,22 +7468,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048143</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048797</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.049992</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.044373</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046044</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04706</v>
       </c>
     </row>
     <row r="126">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -16626,7 +16626,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IPD.xlsx
+++ b/output/pdf_financials_xlsx/IPD.xlsx
@@ -7498,13 +7498,13 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>-0.153222</v>
+        <v>-0.458396</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>-0.151952</v>
+        <v>-0.458081</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.154177</v>
+        <v>-0.308354</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>-0.154177</v>
@@ -7519,7 +7519,7 @@
         <v>-0.156177</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>-0.158927</v>
+        <v>-0.317854</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>-0.158927</v>

--- a/output/pdf_financials_xlsx/IPD.xlsx
+++ b/output/pdf_financials_xlsx/IPD.xlsx
@@ -1281,10 +1281,10 @@
         <v>0.160514</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.063217</v>
+        <v>-0.050217</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.336465</v>
+        <v>-0.327465</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.105782</v>
@@ -1338,10 +1338,10 @@
         <v>-0.115</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.013</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -2016,10 +2016,10 @@
         <v>0.160514</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.063217</v>
+        <v>-0.050217</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.336465</v>
+        <v>-0.327465</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.105782</v>
@@ -2130,10 +2130,10 @@
         <v>0.160514</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.063217</v>
+        <v>-0.050217</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.336465</v>
+        <v>-0.327465</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.105782</v>
@@ -2187,10 +2187,10 @@
         <v>4.34859878965075</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-1.70754258052126</v>
+        <v>-1.356402008416029</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-10.47199857329465</v>
+        <v>-10.19188626693396</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-2.918717543401238</v>
@@ -2244,10 +2244,10 @@
         <v>71.64484094845309</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-25.88764760937531</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.748385323622372</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.952097</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.153585</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -4212,34 +4212,34 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.084309</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.07122000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.072543</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.08026700000000001</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.076332</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.07242899999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.06869699999999999</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.06558</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.06516</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.071247</v>
       </c>
     </row>
     <row r="68">
@@ -6685,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010383</v>
       </c>
     </row>
     <row r="112">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.072173</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.009375</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010383</v>
       </c>
     </row>
     <row r="135">
@@ -8083,7 +8083,7 @@
         <v>0.134288</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.04543</v>
+        <v>-0.055813</v>
       </c>
     </row>
   </sheetData>
@@ -16440,7 +16440,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -18486,7 +18490,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -20028,7 +20036,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -24338,7 +24350,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -36182,7 +36198,11 @@
           <t>Shares repurchase</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -41242,7 +41262,11 @@
           <t>Current income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -41338,7 +41362,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
